--- a/output/pdf_financials_xlsx/WRR.xlsx
+++ b/output/pdf_financials_xlsx/WRR.xlsx
@@ -1156,10 +1156,10 @@
         <v>-1.377304</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.506937</v>
+        <v>-0.506937</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.285997</v>
+        <v>-1.285997</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.622735</v>
@@ -1408,10 +1408,10 @@
         <v>-1.377304</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.506937</v>
+        <v>-0.506937</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.285997</v>
+        <v>-1.285997</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.622735</v>
@@ -1555,10 +1555,10 @@
         <v>-1.377304</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.506937</v>
+        <v>-0.506937</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.285997</v>
+        <v>-1.285997</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.622735</v>
@@ -1759,10 +1759,10 @@
         <v>-1.377304</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.506937</v>
+        <v>-0.506937</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.285997</v>
+        <v>-1.285997</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.622735</v>
@@ -1857,10 +1857,10 @@
         <v>-1.377304</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.506937</v>
+        <v>-0.506937</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.285997</v>
+        <v>-1.285997</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.622735</v>
@@ -1983,10 +1983,10 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -5089,28 +5089,28 @@
         <v>0.773216</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.175162</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.175162</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.474665</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.718632</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.688465</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.657892</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.735992</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.100367</v>
       </c>
     </row>
     <row r="93">
@@ -6315,16 +6315,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.129422</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.045</v>
+        <v>-0.20686</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.07827000000000001</v>
+        <v>-0.290011</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06685000000000001</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-0.116892</v>
@@ -8400,7 +8400,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9230,7 +9234,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -10366,7 +10374,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -10786,7 +10798,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11958,7 +11974,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -21216,7 +21236,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -23468,7 +23492,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
         <v>-0.129422</v>
       </c>
@@ -28425,10 +28453,10 @@
         <v>-1.377304</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>0.506937</v>
+        <v>-0.506937</v>
       </c>
       <c r="M252" s="5" t="n">
-        <v>1.285997</v>
+        <v>-1.285997</v>
       </c>
       <c r="N252" s="5" t="n">
         <v>-0.622735</v>

--- a/output/pdf_financials_xlsx/WRR.xlsx
+++ b/output/pdf_financials_xlsx/WRR.xlsx
@@ -2095,46 +2095,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000675</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.103372</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.03869</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000309</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001273</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.284608</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.126597</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.065636</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.592102</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.455336</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.69062</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.5432709999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.366962</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.205743</v>
       </c>
     </row>
     <row r="35">
@@ -2193,46 +2193,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000675</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.103372</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.03869</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000309</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001273</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.284608</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.126597</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.065636</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.592102</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.455336</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.69062</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.5432709999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.366962</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.205743</v>
       </c>
     </row>
     <row r="37">
@@ -2781,46 +2781,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000675</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.103372</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.03869</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.000309</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.001273</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.284608</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.055713</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.068908</v>
+        <v>0.003272</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.597618</v>
+        <v>0.005516</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.469835</v>
+        <v>0.014499</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.700395</v>
+        <v>0.009775000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.551122</v>
+        <v>0.007851</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.37279</v>
+        <v>0.005828</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.205743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">

--- a/output/pdf_financials_xlsx/WRR.xlsx
+++ b/output/pdf_financials_xlsx/WRR.xlsx
@@ -6434,10 +6434,10 @@
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>0.555764</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>1.18822</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -17414,7 +17414,11 @@
           <t>Issuance of shares, net of issuance cost</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WRR.xlsx
+++ b/output/pdf_financials_xlsx/WRR.xlsx
@@ -3782,28 +3782,28 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.346538</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.491505</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.542276</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.1775</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.275455</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.274144</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.4081</v>
       </c>
     </row>
     <row r="68">
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024309</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7153,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024309</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         <v>-0.213731</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.88583</v>
+        <v>-0.910139</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.08772000000000001</v>
@@ -19424,7 +19424,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -20030,7 +20034,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -22182,7 +22190,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
